--- a/yanfeng/泡泡图DATA/泡泡图当月数据.xlsx
+++ b/yanfeng/泡泡图DATA/泡泡图当月数据.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,65 +487,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30033373-EBP</t>
+          <t>30035161-EBP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30033373-2026,AP,Huawei Anhui,F03F05,Assembly,260030,T,Equipment</t>
+          <t>30035161-2026,AP,BJEV,X90,Lamination,260132,M,Equipment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>赵凯亮</t>
+          <t>路公超</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Meng Zibing_孟子冰(umenz002)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Huawei Anhui,F03F05,Assembly</t>
+          <t>BJEV,X90,Lamination</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05</v>
+        <v>0.115</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>30032261-2026,AP,Huawei Anhui,F03F05,Assembly,000000,1m1T,Equipment</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>30033569-2026,AP,BJEV,X90_IP,Laser,000000,1T,Equipment</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30033376-EBP</t>
+          <t>30034168-EBP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30033376-2026,AP,Huawei Anhui,F05&amp;F03,Assembly,260031,T,Equipment</t>
+          <t>30034168-2026,AP,SVW,A-SUV-mirror,assembly,260008,15T,Equipment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -554,50 +558,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Meng Zibing_孟子冰(umenz002)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Zhou Liwen_周理文(uzhol008)</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Huawei Anhui,F05&amp;F03,Assembly</t>
+          <t>SVW,A-SUV-mirror,assembly</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>30032261-2026,AP,Huawei Anhui,F03F05,Assembly,000000,1m1T,Equipment</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>30031258-2025,AP,SVW,VW Bsuv,vanity mirror,000000,1M1,Equipment</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30034747-EBP</t>
+          <t>30034166-EBP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30034747-2026,AP,Huawei Anhui,X90-DP,260116,Glue spray,M,Equipment</t>
+          <t>30034166-2026,AP,SAIC-GM,C1UL-2,CNSL,Lamination,260073,T,Equipment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -607,7 +614,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -617,97 +624,99 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheng Debao_程德宝(uched025)</t>
+          <t>Fan Aiqiang01_樊爱强(ufana018)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Huawei Anhui,X90-DP,260116</t>
+          <t>SAIC-GM,C1UL-2,CNSL,Lamination</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J4" t="n">
-        <v>-2</v>
+        <v>-15</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>30030766-2025,AP,Huawei Anhui,EHV_DP,Lami,000000,4T,Equipment</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>30033571-2026,AP,SAIC-GM,C1UL-2_CNSL,Lami,000000,2T,Equipment</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30033407-EBP</t>
+          <t>30034746-EBP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30033407-2026,AP,Huawei Anhui,F05/F03 CNSL,Assembly,260036,M,Equipment</t>
+          <t>30034746-2026,AP,Huawei Anhui,X90-DP,260115,glue spray,M,Equipment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>赵凯亮</t>
+          <t>路公超</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Meng Zibing_孟子冰(umenz002)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Cheng Debao_程德宝(uched025)</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Huawei Anhui,F05/F03 CNSL,Assembly</t>
+          <t>Huawei Anhui,X90-DP,260115</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J5" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>30032261-2026,AP,Huawei Anhui,F03F05,Assembly,000000,1m1T,Equipment</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>30030766-2025,AP,Huawei Anhui,EHV_DP,Lami,000000,4T,Equipment</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30034624-EBP</t>
+          <t>30035325-EBP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30034624-2026,AP,BYD,Lamination,260102,M,Equipment</t>
+          <t>30035325-2026,AP,SERES Motors,遮阳板,1200压机,260145,1M,Equipment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -717,111 +726,104 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Huang Linjian_黄琳健(uhual254)</t>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BYD,Lamination</t>
+          <t>SERES Motors,遮阳板,1200压机</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>100</v>
       </c>
       <c r="J6" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.091</v>
+        <v>0.011</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>30027367-2025,AP,BYD,SA3-DP Lam&amp;Wrapping,000000.2M,Equipment</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>30035225-2026,AP,SERES Motors,遮阳板1200压机,000000,1M,Equipment</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>30035089-EBP</t>
+          <t>30034480-EBP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30035089-2026,AP,SAIC-GM,E2LB-2-IP, Automation, 260129, M,Equipment</t>
+          <t>30034480-2028,AP,Toyota,780B,Spraying,260086,T,Equipment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>赵凯亮</t>
+          <t>路公超</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wang Xiaoyu03_王晓宇(uwanx1357)</t>
+          <t>Chen Ziyi01_陈子翌(uchez443)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SAIC-GM,E2LB-2-IP,Automation</t>
+          <t>Toyota,780B,Spraying</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J7" t="n">
         <v>-9</v>
       </c>
       <c r="K7" t="n">
-        <v>0.075</v>
+        <v>0.134</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>30034773-2027,AP,SAIC-GM,E2LB-2-IP,Automation,000000,1M,Equipment</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>1F001051-2023,AP,Toyota,920B,Equipment</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>30033375-EBP</t>
+          <t>30029284-EBP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30033375-2026,AP,Huawei Anhui,F05&amp;F03,Assembly,260032，T,Equipment</t>
+          <t>30029284-2026,AP,SAIC-VW,VW316-9-IP,Automation,250219,M,Equipment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -836,102 +838,104 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Meng Zibing_孟子冰(umenz002)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>Xia Yang_夏阳(uxiay057)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Hao Xiuxia_郝秀霞(uhaox031)</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Huawei Anhui,F05&amp;F03</t>
+          <t>SAIC-VW,VW316-9-IP,Automation</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>100</v>
       </c>
       <c r="J8" t="n">
-        <v>-9</v>
+        <v>-15</v>
       </c>
       <c r="K8" t="n">
-        <v>0.05</v>
+        <v>0.205</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>30032261-2026,AP,Huawei Anhui,F03F05,Assembly,000000,1m1T,Equipment</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>30027751-2025,AP,SAIC-VW,VW316-9IP,Automation,000000,1M2T,Equipment</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>30034623-EBP</t>
+          <t>30033461-EBP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30034623-2026,AP,BYD,Glue,260103,M,Equipment</t>
+          <t>30033461-2026,AP,SVW,B-SUV-mirror,assy,260041,1M,Equipment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>路公超</t>
+          <t>赵凯亮</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chen Jie04_陈洁(uchej018)</t>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>BYD,Glue</t>
+          <t>SVW,B-SUV-mirror,assy</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J9" t="n">
-        <v>-2</v>
+        <v>-11</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>30032880-2026,AP,BYD,广州，Roll rubber,000000,1M,Equipment</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>30031258-2025,AP,SVW,VW Bsuv,vanity mirror,000000,1M1,Equipment</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>30033405-EBP</t>
+          <t>30034477-EBP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>30033405-2026,AP,Huawei Anhui,F05 IP,Assembly,260038,M,Equipment</t>
+          <t>30034477-2025,AP,Toyota,780B-DP,Flaming, 260079,M,Equipment</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -941,164 +945,160 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Meng Zibing_孟子冰(umenz002)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Huawei Anhui,F05 IP,Assembly</t>
+          <t>Toyota,780B-DP,Flaming</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J10" t="n">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="K10" t="n">
-        <v>0.05</v>
+        <v>0.134</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30032261-2026,AP,Huawei Anhui,F03F05,Assembly,000000,1m1T,Equipment</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>1F001051-2023,AP,Toyota,920B,Equipment</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>30033404-EBP</t>
+          <t>30033409-EBP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30033404-2026,AP,VW Group,VW426-DP,Lamination,260033,M,Equipment</t>
+          <t>30033409-2026,AP,Huawei Anhui,F05/F03 CNSL,Assembly,260037,M,Equipment</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>路公超</t>
+          <t>赵凯亮</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Huang Linjian_黄琳健(uhual254)</t>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>VW Group,VW426-DP,Lamination</t>
+          <t>Huawei Anhui,F05/F03 CNSL,Assembly</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="K11" t="n">
-        <v>0.169</v>
+        <v>0.05</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>30019456-2025,AP,VW Group,VW426-IP,Auto cell,000000,1M,Equipment</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>30032261-2026,AP,Huawei Anhui,F03F05,Assembly,000000,1m1T,Equipment</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>30032370-EBP</t>
+          <t>30031537-EBP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>30032370-2026,AP,SERES Motors,F3_Seat rail,Assy,250379,Equipment</t>
+          <t>30031537-2026,AP,Huawei Anhui,EHV-DP,Lamination,250338,T,Equipment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>赵凯亮</t>
+          <t>路公超</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yang Yang28_杨阳(uyany430)</t>
+          <t>Xia Yang_夏阳(uxiay057)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Huang Dinghui_黄定辉(uhuad002)</t>
+          <t>Fan Aiqiang01_樊爱强(ufana018)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>SERES Motors,F3_Seat rail</t>
+          <t>Huawei Anhui,EHV-DP,Lamination</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J12" t="n">
-        <v>-7</v>
+        <v>-30</v>
       </c>
       <c r="K12" t="n">
-        <v>0.334</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>30030599-2026,AP,SERES Motors,F3_Seat rail,Assy,000000,1M,Equipment</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>30030766-2025,AP,Huawei Anhui,EHV_DP,Lami,000000,4T,Equipment</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>30032706-EBP</t>
+          <t>30030761-EBP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>30032706-2025,AP,SERES Motors,A15-mirror, assy, 260006, 15T,Equipment</t>
+          <t>30030761-2025,AP,SAIC-VW,VW416-IP,Automatin,250306,M,,Equipment</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1108,44 +1108,685 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wang Baowei_王保卫(uwanb363)</t>
+          <t>Xia Yang_夏阳(uxiay057)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wang Wanfang_王万芳(uwanw356)</t>
+          <t>Liu Jinghua01_刘璟华(uliuj595)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SERES Motors,A15-mirror,assy</t>
+          <t>SAIC-VW,VW416-IP,Automatin,250306</t>
         </is>
       </c>
       <c r="I13" t="n">
         <v>100</v>
       </c>
       <c r="J13" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>30027751-2025,AP,SAIC-VW,VW316-9IP,Automation,000000,1M2T,Equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>30035209-EBP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>30035209-2026,AP,Jianghuai,C673-DP,Foam sticking,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>赵凯亮</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Jianghuai,C673-DP</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>100</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>30030795-2026,AP,Jianghuai,JH-A Roller glue,000000,1M,Equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>30034615-EBP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>30034615-2026,AP,BYD,MR&amp;ST-IP, Glue,260091, M,Equipment</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>路公超</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Yuan Shuai_袁帅(uyuas003)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>BYD,MR&amp;ST-IP,Glue</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>90</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>30017103-2024,AP,BYD,BYD MR-IP,Prefixture,000000,2T,Equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>30033578-EBP</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>30033578-2026,AP,Tes,TBD_Click Rim, Lami, 260050, T,Equipment</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>路公超</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Zhou Huasheng_周华盛(uzhoh176)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Tes,TBD_Click Rim,Lami</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>100</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>30028949-2026,AP,Tes,TBD_Click RIM,Lami,000000,1T,Equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>30034171-EBP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>30034171-2026,AP,Jianghuai,JHC-sun visor,assy, 260074, NT,Equipment</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>赵凯亮</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Jianghuai,JHC-sun visor,assy</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>100</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>30030795-2026,AP,Jianghuai,JH-A Roller glue,000000,1M,Equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>30033723-EBP</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>30033723-2026,AP,VW Group,VW426 PAB Chute Cell CI,260042,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>赵凯亮</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Wei Shaoguan_韦少官(uweis086)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>VW Group,VW426 PAB Chute Cell CI</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>90</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>30019456-2025,AP,VW Group,VW426-IP,Auto cell,000000,1M,Equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>30031541-EBP</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>30031541-2026,AP,Huawei Anhui,EHV-DP,Lamination,250340,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>路公超</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Xia Yang_夏阳(uxiay057)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Huawei Anhui,EHV-DP,Lamination</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>100</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-30</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>30030766-2025,AP,Huawei Anhui,EHV_DP,Lami,000000,4T,Equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>30031540-EBP</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>30031540-2026,AP,Huawei Anhui,EHV-DP,Lamination,250339,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>路公超</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Xia Yang_夏阳(uxiay057)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fan Aiqiang01_樊爱强(ufana018)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Huawei Anhui,EHV-DP,Lamination</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>100</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-30</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>30030766-2025,AP,Huawei Anhui,EHV_DP,Lami,000000,4T,Equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>30032991-EBP</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>30032991-2026,AP,Jianghuai,JH-C-mirror,assembly,260009,14T,Equipment</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>赵凯亮</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Zhang Shuai27_张帅(uzhas1129)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Jianghuai,JH-C-mirror,assembly</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>90</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-12</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>30030795-2026,AP,Jianghuai,JH-A Roller glue,000000,1M,Equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>30035208-EBP</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>30035208-2026,AP,Jianghuai,C673-DP,Foam Sticking,260140,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>赵凯亮</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Jianghuai,C673-DP,Foam Sticking</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>100</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>30030795-2026,AP,Jianghuai,JH-A Roller glue,000000,1M,Equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>30031304-EBP</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>30031304-2026,AP,Chery,EHV-Pilla,Welding,250319,1M,Equipment</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>赵凯亮</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Xia Yang_夏阳(uxiay057)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Huang Sheng02_黄圣(uhuas068)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Chery,EHV-Pilla,Welding</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>100</v>
+      </c>
+      <c r="J23" t="n">
         <v>-16</v>
       </c>
-      <c r="K13" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>30029682-2026,AP,SERES Motors,A15-Other,Assembly,000000,1M,Equipment</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>30030391-2026,AP,Chery,EHV-Pillar,Welding,000000,1M,Equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>30029921-EBP</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>30029921-2026,AP,Tes,Highland-FC, Assembly,250246,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>赵凯亮</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Li Yanchen_李彦辰(ulixy466)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Tes,Highland-FC,Assembly</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>100</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-26</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>30028749-2025,AP,Tes,Highland-FC,Trans MX,000000,1M9T,Equipment</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Design_release</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
